--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:08</t>
+    <t xml:space="preserve">2026-09-09 23:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:02</t>
+    <t xml:space="preserve">2026-09-17 13:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:59</t>
+    <t xml:space="preserve">2026-09-23 12:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:28</t>
+    <t xml:space="preserve">2026-10-02 13:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_biobio.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Arauco</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">San Rosendo</t>
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Lota</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Quilaco</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:47</t>
+    <t xml:space="preserve">2026-10-04 08:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:49</t>
+    <t xml:space="preserve">2026-10-05 10:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -631,7 +631,7 @@
         <v>2020</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>860361.62</v>
+        <v>860361.63</v>
       </c>
     </row>
     <row r="6">
@@ -733,7 +733,7 @@
         <v>2020</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>784800.62</v>
+        <v>784800.63</v>
       </c>
     </row>
     <row r="12">
@@ -835,7 +835,7 @@
         <v>2020</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>697689.62</v>
+        <v>697689.63</v>
       </c>
     </row>
     <row r="18">
